--- a/artfynd/A 74002-2021 artfynd.xlsx
+++ b/artfynd/A 74002-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 74002-2021 artfynd.xlsx
+++ b/artfynd/A 74002-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AY26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>65409693</v>
+        <v>65409663</v>
       </c>
       <c r="B2" t="n">
-        <v>77605</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79422</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>422465.785334088</v>
+        <v>422518</v>
       </c>
       <c r="R2" t="n">
-        <v>6839699.849170378</v>
+        <v>6839584</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -752,19 +747,9 @@
           <t>2015-09-16</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2015-09-16</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
@@ -796,15 +781,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>65409663</v>
+        <v>65409688</v>
       </c>
       <c r="B3" t="n">
-        <v>77605</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79422</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -840,10 +820,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>422517.8728748599</v>
+        <v>422612</v>
       </c>
       <c r="R3" t="n">
-        <v>6839584.239529775</v>
+        <v>6839286</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -873,19 +853,9 @@
           <t>2015-09-16</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2015-09-16</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -917,15 +887,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>65409688</v>
+        <v>65409693</v>
       </c>
       <c r="B4" t="n">
-        <v>77605</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79422</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -961,10 +926,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>422611.9876490716</v>
+        <v>422466</v>
       </c>
       <c r="R4" t="n">
-        <v>6839285.803708973</v>
+        <v>6839700</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -994,19 +959,9 @@
           <t>2015-09-16</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2015-09-16</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
@@ -1038,50 +993,48 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>100212695</v>
+        <v>100212652</v>
       </c>
       <c r="B5" t="n">
-        <v>77665</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79422</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229569</v>
+        <v>967</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Varglavsknöl</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phacopsis vulpina</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Tul.</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Översjökölen, Dlr</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>422464.6085220666</v>
+        <v>422555</v>
       </c>
       <c r="R5" t="n">
-        <v>6839520.858071295</v>
+        <v>6839434</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1111,29 +1064,25 @@
           <t>2022-04-12</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-04-12</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Urskogsartad myr</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1143,22 +1092,17 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Andreas Öster, John-Olof Halvarsson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>100212716</v>
+        <v>100212670</v>
       </c>
       <c r="B6" t="n">
-        <v>76486</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79422</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1166,21 +1110,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6487</v>
+        <v>967</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blågrå svartspik</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Chaenothecopsis fennica</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Laurila) Tibell</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1190,10 +1134,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>422405.3562289648</v>
+        <v>422467</v>
       </c>
       <c r="R6" t="n">
-        <v>6839698.361361461</v>
+        <v>6839701</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1223,19 +1167,9 @@
           <t>2022-04-12</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-04-12</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1262,15 +1196,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>100212638</v>
+        <v>100212673</v>
       </c>
       <c r="B7" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79422</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1278,37 +1207,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>967</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Översjökölen, Dlr</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>422239.035252378</v>
+        <v>422456</v>
       </c>
       <c r="R7" t="n">
-        <v>6839724.905417613</v>
+        <v>6839729</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1338,35 +1264,19 @@
           <t>2022-04-12</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2022-04-12</t>
         </is>
       </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>Urskogsartad myr</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
@@ -1376,22 +1286,17 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Andreas Öster, John-Olof Halvarsson</t>
+          <t>Andreas Öster</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>100212652</v>
+        <v>100212678</v>
       </c>
       <c r="B8" t="n">
-        <v>77605</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79422</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1417,19 +1322,16 @@
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Översjökölen, Dlr</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>422554.9244210609</v>
+        <v>422645</v>
       </c>
       <c r="R8" t="n">
-        <v>6839434.299674612</v>
+        <v>6839499</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1459,35 +1361,19 @@
           <t>2022-04-12</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2022-04-12</t>
         </is>
       </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
-      </c>
-      <c r="AI8" t="inlineStr">
-        <is>
-          <t>Urskogsartad myr</t>
-        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
@@ -1497,22 +1383,17 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Andreas Öster, John-Olof Halvarsson</t>
+          <t>Andreas Öster</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>100212678</v>
+        <v>100212698</v>
       </c>
       <c r="B9" t="n">
-        <v>77605</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79422</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1544,10 +1425,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>422644.8430321877</v>
+        <v>422651</v>
       </c>
       <c r="R9" t="n">
-        <v>6839499.234840628</v>
+        <v>6839471</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1577,19 +1458,9 @@
           <t>2022-04-12</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2022-04-12</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1616,15 +1487,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>100212721</v>
+        <v>100212708</v>
       </c>
       <c r="B10" t="n">
-        <v>77605</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79422</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1656,10 +1522,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>422493.8072466771</v>
+        <v>422518</v>
       </c>
       <c r="R10" t="n">
-        <v>6839571.485254872</v>
+        <v>6839581</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1689,19 +1555,9 @@
           <t>2022-04-12</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2022-04-12</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1728,15 +1584,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>100212673</v>
+        <v>100212709</v>
       </c>
       <c r="B11" t="n">
-        <v>77605</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79422</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1768,10 +1619,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>422455.9696834275</v>
+        <v>422543</v>
       </c>
       <c r="R11" t="n">
-        <v>6839728.560213988</v>
+        <v>6839572</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1801,19 +1652,9 @@
           <t>2022-04-12</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2022-04-12</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1840,15 +1681,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>100212708</v>
+        <v>100212721</v>
       </c>
       <c r="B12" t="n">
-        <v>77605</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79422</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1880,10 +1716,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>422517.78744189</v>
+        <v>422494</v>
       </c>
       <c r="R12" t="n">
-        <v>6839580.44264241</v>
+        <v>6839571</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1913,19 +1749,9 @@
           <t>2022-04-12</t>
         </is>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA12" t="inlineStr">
         <is>
           <t>2022-04-12</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1952,15 +1778,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>100212709</v>
+        <v>100212724</v>
       </c>
       <c r="B13" t="n">
-        <v>77605</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79422</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1992,10 +1813,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>422542.7984982944</v>
+        <v>422429</v>
       </c>
       <c r="R13" t="n">
-        <v>6839571.807482114</v>
+        <v>6839993</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2025,19 +1846,9 @@
           <t>2022-04-12</t>
         </is>
       </c>
-      <c r="Z13" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA13" t="inlineStr">
         <is>
           <t>2022-04-12</t>
-        </is>
-      </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2064,15 +1875,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>100212753</v>
+        <v>100212733</v>
       </c>
       <c r="B14" t="n">
-        <v>78072</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79422</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2080,21 +1886,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>229821</v>
+        <v>967</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2104,10 +1910,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>422629.530380877</v>
+        <v>422456</v>
       </c>
       <c r="R14" t="n">
-        <v>6839368.039631277</v>
+        <v>6839675</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2137,19 +1943,9 @@
           <t>2022-04-12</t>
         </is>
       </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA14" t="inlineStr">
         <is>
           <t>2022-04-12</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2176,15 +1972,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>100212662</v>
+        <v>100212734</v>
       </c>
       <c r="B15" t="n">
-        <v>77258</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79422</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2192,21 +1983,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6446</v>
+        <v>967</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Varglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Letharia vulpina</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hue</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2216,10 +2007,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>422609.667295931</v>
+        <v>422606</v>
       </c>
       <c r="R15" t="n">
-        <v>6839351.865106448</v>
+        <v>6839396</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2249,19 +2040,9 @@
           <t>2022-04-12</t>
         </is>
       </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA15" t="inlineStr">
         <is>
           <t>2022-04-12</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2288,15 +2069,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>100212734</v>
+        <v>100212714</v>
       </c>
       <c r="B16" t="n">
-        <v>77605</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>81312</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2304,21 +2080,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>967</v>
+        <v>1049</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Kortskaftad ärgspik</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Microcalicium ahlneri</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>Tibell</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2328,10 +2104,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>422606.3703792237</v>
+        <v>422455</v>
       </c>
       <c r="R16" t="n">
-        <v>6839395.628084918</v>
+        <v>6839729</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2361,19 +2137,9 @@
           <t>2022-04-12</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2022-04-12</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2400,50 +2166,48 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>100212733</v>
+        <v>100212638</v>
       </c>
       <c r="B17" t="n">
-        <v>77605</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>967</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
           <t>Översjökölen, Dlr</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>422455.7125934964</v>
+        <v>422239</v>
       </c>
       <c r="R17" t="n">
-        <v>6839674.909619728</v>
+        <v>6839725</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2473,29 +2237,25 @@
           <t>2022-04-12</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2022-04-12</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD17" t="b">
         <v>0</v>
       </c>
       <c r="AE17" t="b">
         <v>0</v>
       </c>
+      <c r="AF17" t="inlineStr"/>
       <c r="AG17" t="b">
         <v>0</v>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Urskogsartad myr</t>
+        </is>
       </c>
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
@@ -2505,7 +2265,7 @@
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Andreas Öster, John-Olof Halvarsson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2515,16 +2275,11 @@
         <v>100212732</v>
       </c>
       <c r="B18" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -2552,10 +2307,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>422411.1371912179</v>
+        <v>422411</v>
       </c>
       <c r="R18" t="n">
-        <v>6839975.99903131</v>
+        <v>6839976</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2585,19 +2340,9 @@
           <t>2022-04-12</t>
         </is>
       </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA18" t="inlineStr">
         <is>
           <t>2022-04-12</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2624,15 +2369,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>100212714</v>
+        <v>100212662</v>
       </c>
       <c r="B19" t="n">
-        <v>79433</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2640,21 +2380,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1049</v>
+        <v>6446</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Kortskaftad ärgspik</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Microcalicium ahlneri</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>Tibell</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2664,10 +2404,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>422455.0190622803</v>
+        <v>422610</v>
       </c>
       <c r="R19" t="n">
-        <v>6839728.581622097</v>
+        <v>6839352</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2697,19 +2437,9 @@
           <t>2022-04-12</t>
         </is>
       </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA19" t="inlineStr">
         <is>
           <t>2022-04-12</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2736,15 +2466,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>100212697</v>
+        <v>100212659</v>
       </c>
       <c r="B20" t="n">
-        <v>77259</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2752,34 +2477,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>228912</v>
+        <v>6453</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="N20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
           <t>Översjökölen, Dlr</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>422628.4132060144</v>
+        <v>422434</v>
       </c>
       <c r="R20" t="n">
-        <v>6839529.99496722</v>
+        <v>6839824</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2809,21 +2537,11 @@
           <t>2022-04-12</t>
         </is>
       </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA20" t="inlineStr">
         <is>
           <t>2022-04-12</t>
         </is>
       </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD20" t="b">
         <v>0</v>
       </c>
@@ -2832,6 +2550,11 @@
       </c>
       <c r="AG20" t="b">
         <v>0</v>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>Urskogsartad myr</t>
+        </is>
       </c>
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
@@ -2841,22 +2564,17 @@
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Andreas Öster</t>
+          <t>Andreas Öster, John-Olof Halvarsson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>100212698</v>
+        <v>100212666</v>
       </c>
       <c r="B21" t="n">
-        <v>77605</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79946</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2864,21 +2582,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>967</v>
+        <v>6453</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Varglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Letharia vulpina</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) Hue</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2888,10 +2606,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>422651.3441886021</v>
+        <v>422373</v>
       </c>
       <c r="R21" t="n">
-        <v>6839471.071856513</v>
+        <v>6839744</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2921,19 +2639,9 @@
           <t>2022-04-12</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2022-04-12</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2960,15 +2668,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>100212666</v>
+        <v>100212716</v>
       </c>
       <c r="B22" t="n">
-        <v>78098</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78334</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2976,21 +2679,21 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6453</v>
+        <v>6487</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Blågrå svartspik</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Chaenothecopsis fennica</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Laurila) Tibell</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3000,10 +2703,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>422373.0899274306</v>
+        <v>422406</v>
       </c>
       <c r="R22" t="n">
-        <v>6839743.722930838</v>
+        <v>6839698</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3033,19 +2736,9 @@
           <t>2022-04-12</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2022-04-12</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3072,15 +2765,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>100212737</v>
+        <v>100212697</v>
       </c>
       <c r="B23" t="n">
-        <v>78072</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79085</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3088,21 +2776,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3112,10 +2800,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>422452.6237852367</v>
+        <v>422629</v>
       </c>
       <c r="R23" t="n">
-        <v>6839537.747999968</v>
+        <v>6839530</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3145,19 +2833,9 @@
           <t>2022-04-12</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2022-04-12</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3181,6 +2859,297 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>100212695</v>
+      </c>
+      <c r="B24" t="n">
+        <v>79483</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>229569</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Varglavsknöl</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Phacopsis vulpina</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>Tul.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Översjökölen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>422465</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6839521</v>
+      </c>
+      <c r="S24" t="n">
+        <v>25</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2022-04-12</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2022-04-12</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>100212737</v>
+      </c>
+      <c r="B25" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Översjökölen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>422452</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6839538</v>
+      </c>
+      <c r="S25" t="n">
+        <v>25</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2022-04-12</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2022-04-12</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>100212753</v>
+      </c>
+      <c r="B26" t="n">
+        <v>79917</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>229821</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Vedflamlav</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Ramboldia elabens</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Översjökölen, Dlr</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>422629</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6839368</v>
+      </c>
+      <c r="S26" t="n">
+        <v>25</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Härjedalen</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Lillhärdal</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2022-04-12</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2022-04-12</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Andreas Öster</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 74002-2021 artfynd.xlsx
+++ b/artfynd/A 74002-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY26"/>
+  <dimension ref="A1:AZ26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/65409663</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/65409688</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -990,6 +1005,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/65409693</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1096,6 +1116,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100212652</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1193,6 +1218,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100212670</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1290,6 +1320,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100212673</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1387,6 +1422,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100212678</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1484,6 +1524,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100212698</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1581,6 +1626,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100212708</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1678,6 +1728,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100212709</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1775,6 +1830,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100212721</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1872,6 +1932,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100212724</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1969,6 +2034,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100212733</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2066,6 +2136,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100212734</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2163,6 +2238,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100212714</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2269,6 +2349,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100212638</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2366,6 +2451,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100212732</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2463,6 +2553,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100212662</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2568,6 +2663,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100212659</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2665,6 +2765,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100212666</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2762,6 +2867,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100212716</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2859,6 +2969,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100212697</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -2956,6 +3071,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100212695</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3053,6 +3173,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100212737</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3150,8 +3275,40 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100212753</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>